--- a/docs/downloads/10/tbl_ef_vente_alaotra_tous.xlsx
+++ b/docs/downloads/10/tbl_ef_vente_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -405,7 +405,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -468,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -483,7 +483,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -732,7 +732,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -840,7 +840,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -882,7 +882,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
